--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8928,0.0368,0.0154,0.0101</t>
-  </si>
-  <si>
-    <t>0.9435,0.0117,0.0185,0.0062</t>
-  </si>
-  <si>
-    <t>0.9774,0.0085,0.0042,0.0007</t>
-  </si>
-  <si>
-    <t>0.9808,0.0065,0.0043,0.0010</t>
-  </si>
-  <si>
-    <t>0.7569,0.1409,0.0165,0.0138</t>
-  </si>
-  <si>
-    <t>0.9619,0.0144,0.0022,0.0047</t>
-  </si>
-  <si>
-    <t>0.9587,0.0278,0.0038,0.0010</t>
-  </si>
-  <si>
-    <t>0.9366,0.0316,0.0020,0.0029</t>
-  </si>
-  <si>
-    <t>0.8454,0.0933,0.0046,0.0084</t>
-  </si>
-  <si>
-    <t>0.7517,0.1968,0.0077,0.0052</t>
-  </si>
-  <si>
-    <t>0.8563,0.1228,0.0038,0.0023</t>
-  </si>
-  <si>
-    <t>0.9121,0.0502,0.0032,0.0032</t>
-  </si>
-  <si>
-    <t>0.9873,0.0054,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.9730,0.0134,0.0031,0.0003</t>
-  </si>
-  <si>
-    <t>0.9786,0.0065,0.0041,0.0006</t>
-  </si>
-  <si>
-    <t>0.9867,0.0012,0.0195,0.0001</t>
-  </si>
-  <si>
-    <t>0.9911,0.0014,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.7491,0.3651,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.7669,0.3319,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.8636,0.1281,0.0205,0.0028</t>
-  </si>
-  <si>
-    <t>0.8882,0.1418,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.1193,0.9113,0.0021,0.0006</t>
-  </si>
-  <si>
-    <t>0.9966,0.0003,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9840,0.0017,0.0144,0.0002</t>
-  </si>
-  <si>
-    <t>0.9054,0.0056,0.1980,0.0010</t>
-  </si>
-  <si>
-    <t>0.9788,0.0046,0.0179,0.0003</t>
-  </si>
-  <si>
-    <t>0.9911,0.0021,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.9899,0.0026,0.0044,0.0001</t>
-  </si>
-  <si>
-    <t>0.8344,0.0171,0.2519,0.0021</t>
-  </si>
-  <si>
-    <t>0.9725,0.0367,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.9207,0.0943,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.0415,0.2580,0.8989,0.0068</t>
-  </si>
-  <si>
-    <t>0.9023,0.1870,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9497,0.0407,0.0046,0.0010</t>
-  </si>
-  <si>
-    <t>0.8508,0.1274,0.0339,0.0033</t>
-  </si>
-  <si>
-    <t>0.9587,0.0428,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9587,0.0354,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.1025,0.6844,0.6387,0.0040</t>
-  </si>
-  <si>
-    <t>0.4395,0.2509,0.4395,0.0028</t>
-  </si>
-  <si>
-    <t>0.7751,0.0976,0.0996,0.0017</t>
-  </si>
-  <si>
-    <t>0.9539,0.0058,0.0271,0.0046</t>
-  </si>
-  <si>
-    <t>0.9663,0.0152,0.0141,0.0002</t>
-  </si>
-  <si>
-    <t>0.9498,0.0293,0.0234,0.0011</t>
-  </si>
-  <si>
-    <t>0.9237,0.0295,0.0399,0.0004</t>
-  </si>
-  <si>
-    <t>0.9851,0.0089,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.9818,0.0100,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.7630,0.2938,0.0135,0.0007</t>
-  </si>
-  <si>
-    <t>0.5669,0.5297,0.0141,0.0008</t>
-  </si>
-  <si>
-    <t>0.5104,0.2131,0.4464,0.0176</t>
-  </si>
-  <si>
-    <t>0.1864,0.3656,0.7132,0.0026</t>
-  </si>
-  <si>
-    <t>0.9769,0.0038,0.0212,0.0005</t>
-  </si>
-  <si>
-    <t>0.8291,0.0612,0.0768,0.0009</t>
-  </si>
-  <si>
-    <t>0.5011,0.0555,0.5106,0.0009</t>
-  </si>
-  <si>
-    <t>0.9496,0.0180,0.0270,0.0003</t>
-  </si>
-  <si>
-    <t>0.8794,0.0627,0.0053,0.0082</t>
-  </si>
-  <si>
-    <t>0.8279,0.1783,0.0079,0.0022</t>
-  </si>
-  <si>
-    <t>0.9126,0.0807,0.0065,0.0024</t>
-  </si>
-  <si>
-    <t>0.7752,0.0931,0.2003,0.0066</t>
-  </si>
-  <si>
-    <t>0.9057,0.0850,0.0065,0.0052</t>
-  </si>
-  <si>
-    <t>0.8977,0.0920,0.0065,0.0044</t>
-  </si>
-  <si>
-    <t>0.9175,0.0783,0.0040,0.0008</t>
-  </si>
-  <si>
-    <t>0.0048,0.9516,0.9306,0.0016</t>
-  </si>
-  <si>
-    <t>0.9201,0.0130,0.1153,0.0009</t>
-  </si>
-  <si>
-    <t>0.7861,0.0207,0.3407,0.0009</t>
-  </si>
-  <si>
-    <t>0.0515,0.8605,0.5697,0.0008</t>
-  </si>
-  <si>
-    <t>0.1780,0.2804,0.6795,0.0012</t>
-  </si>
-  <si>
-    <t>0.9105,0.1908,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.1556,0.9399,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.9656,0.0232,0.0046,0.0013</t>
-  </si>
-  <si>
-    <t>0.9914,0.0053,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.7429,0.1394,0.1018,0.0013</t>
-  </si>
-  <si>
-    <t>0.2607,0.6660,0.1403,0.0008</t>
-  </si>
-  <si>
-    <t>0.2167,0.5866,0.3460,0.0011</t>
-  </si>
-  <si>
-    <t>0.0340,0.9233,0.4539,0.0008</t>
-  </si>
-  <si>
-    <t>0.0045,0.9454,0.9146,0.0006</t>
-  </si>
-  <si>
-    <t>0.9249,0.0094,0.0762,0.0046</t>
-  </si>
-  <si>
-    <t>0.9825,0.0026,0.0051,0.0024</t>
-  </si>
-  <si>
-    <t>0.9745,0.0048,0.0057,0.0031</t>
-  </si>
-  <si>
-    <t>0.9246,0.0235,0.0257,0.0062</t>
-  </si>
-  <si>
-    <t>0.9828,0.0051,0.0048,0.0007</t>
-  </si>
-  <si>
-    <t>0.9857,0.0022,0.0038,0.0011</t>
-  </si>
-  <si>
-    <t>0.0035,0.9744,0.8528,0.0005</t>
-  </si>
-  <si>
-    <t>0.0844,0.6819,0.7084,0.0018</t>
-  </si>
-  <si>
-    <t>0.4733,0.3347,0.2458,0.0029</t>
-  </si>
-  <si>
-    <t>0.7002,0.2156,0.0672,0.0005</t>
-  </si>
-  <si>
-    <t>0.1829,0.7532,0.2215,0.0024</t>
-  </si>
-  <si>
-    <t>0.1103,0.7926,0.4019,0.0023</t>
-  </si>
-  <si>
-    <t>0.9445,0.0413,0.0025,0.0013</t>
-  </si>
-  <si>
-    <t>0.8819,0.0915,0.0093,0.0043</t>
-  </si>
-  <si>
-    <t>0.9683,0.0149,0.0031,0.0022</t>
-  </si>
-  <si>
-    <t>0.8657,0.1312,0.0082,0.0022</t>
-  </si>
-  <si>
-    <t>0.9582,0.0205,0.0016,0.0021</t>
-  </si>
-  <si>
-    <t>0.8816,0.0498,0.0046,0.0114</t>
-  </si>
-  <si>
-    <t>0.7814,0.1827,0.0110,0.0060</t>
-  </si>
-  <si>
-    <t>0.8615,0.1453,0.0018,0.0013</t>
-  </si>
-  <si>
-    <t>0.9173,0.0225,0.0045,0.0098</t>
-  </si>
-  <si>
-    <t>0.9739,0.0182,0.0025,0.0010</t>
-  </si>
-  <si>
-    <t>0.9902,0.0048,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.8021,0.1807,0.0068,0.0035</t>
-  </si>
-  <si>
-    <t>0.9452,0.0382,0.0028,0.0016</t>
-  </si>
-  <si>
-    <t>0.8727,0.1269,0.0048,0.0030</t>
-  </si>
-  <si>
-    <t>0.8360,0.1110,0.0180,0.0149</t>
-  </si>
-  <si>
-    <t>0.9663,0.0166,0.0022,0.0024</t>
-  </si>
-  <si>
-    <t>0.4687,0.0120,0.7930,0.0004</t>
-  </si>
-  <si>
-    <t>0.9570,0.0198,0.0127,0.0005</t>
-  </si>
-  <si>
-    <t>0.9909,0.0018,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.9902,0.0014,0.0053,0.0004</t>
-  </si>
-  <si>
-    <t>0.5477,0.5558,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.4562,0.6884,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9214,0.0994,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.7136,0.3401,0.0086,0.0025</t>
-  </si>
-  <si>
-    <t>0.1792,0.8704,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.2912,0.8513,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.7462,0.2675,0.0202,0.0045</t>
-  </si>
-  <si>
-    <t>0.9902,0.0041,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9632,0.0057,0.0298,0.0011</t>
-  </si>
-  <si>
-    <t>0.9856,0.0021,0.0070,0.0005</t>
-  </si>
-  <si>
-    <t>0.9751,0.0093,0.0078,0.0002</t>
-  </si>
-  <si>
-    <t>0.9500,0.0325,0.0069,0.0006</t>
-  </si>
-  <si>
-    <t>0.9839,0.0143,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.2719,0.8483,0.0064,0.0002</t>
-  </si>
-  <si>
-    <t>0.9224,0.0855,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.0783,0.9225,0.0672,0.0011</t>
-  </si>
-  <si>
-    <t>0.9626,0.0344,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.9739,0.0360,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.8925,0.1278,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9875,0.0070,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9538,0.0432,0.0031,0.0010</t>
-  </si>
-  <si>
-    <t>0.7980,0.1235,0.0150,0.0123</t>
-  </si>
-  <si>
-    <t>0.9027,0.0439,0.0039,0.0048</t>
-  </si>
-  <si>
-    <t>0.5267,0.3658,0.0363,0.0383</t>
-  </si>
-  <si>
-    <t>0.9177,0.0547,0.0115,0.0051</t>
-  </si>
-  <si>
-    <t>0.9360,0.0484,0.0038,0.0018</t>
-  </si>
-  <si>
-    <t>0.9166,0.0415,0.0047,0.0058</t>
-  </si>
-  <si>
-    <t>0.8439,0.0719,0.0735,0.0007</t>
-  </si>
-  <si>
-    <t>0.7715,0.1109,0.1120,0.0012</t>
-  </si>
-  <si>
-    <t>0.3703,0.2136,0.3945,0.0014</t>
-  </si>
-  <si>
-    <t>0.7449,0.1114,0.1492,0.0021</t>
-  </si>
-  <si>
-    <t>0.9921,0.0012,0.0054,0.0002</t>
-  </si>
-  <si>
-    <t>0.9652,0.0038,0.0332,0.0015</t>
-  </si>
-  <si>
-    <t>0.9846,0.0056,0.0044,0.0004</t>
-  </si>
-  <si>
-    <t>0.9864,0.0026,0.0033,0.0006</t>
-  </si>
-  <si>
-    <t>0.9750,0.0048,0.0085,0.0018</t>
-  </si>
-  <si>
-    <t>0.7956,0.0056,0.0328,0.0886</t>
-  </si>
-  <si>
-    <t>0.9691,0.0044,0.0159,0.0038</t>
-  </si>
-  <si>
-    <t>0.9687,0.0052,0.0144,0.0030</t>
-  </si>
-  <si>
-    <t>0.3450,0.4857,0.2925,0.0023</t>
-  </si>
-  <si>
-    <t>0.9454,0.0261,0.0036,0.0053</t>
-  </si>
-  <si>
-    <t>0.8608,0.0909,0.0142,0.0039</t>
-  </si>
-  <si>
-    <t>0.9780,0.0088,0.0036,0.0013</t>
-  </si>
-  <si>
-    <t>0.9119,0.0742,0.0106,0.0019</t>
-  </si>
-  <si>
-    <t>0.9102,0.0474,0.0061,0.0049</t>
-  </si>
-  <si>
-    <t>0.9855,0.0062,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.6320,0.3681,0.0072,0.0027</t>
-  </si>
-  <si>
-    <t>0.4166,0.3102,0.4202,0.0493</t>
-  </si>
-  <si>
-    <t>0.9739,0.0229,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.9295,0.0336,0.0053,0.0039</t>
-  </si>
-  <si>
-    <t>0.9071,0.1313,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9866,0.0046,0.0024,0.0004</t>
-  </si>
-  <si>
-    <t>0.9683,0.0242,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.8825,0.1041,0.0049,0.0007</t>
-  </si>
-  <si>
-    <t>0.9874,0.0062,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.9894,0.0027,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.9164,0.0748,0.0042,0.0016</t>
-  </si>
-  <si>
-    <t>0.8704,0.1042,0.0040,0.0023</t>
-  </si>
-  <si>
-    <t>0.9660,0.0203,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.8815,0.0600,0.0080,0.0082</t>
-  </si>
-  <si>
-    <t>0.9057,0.0638,0.0073,0.0022</t>
-  </si>
-  <si>
-    <t>0.9567,0.0312,0.0033,0.0010</t>
-  </si>
-  <si>
-    <t>0.8991,0.0570,0.0153,0.0111</t>
-  </si>
-  <si>
-    <t>0.8111,0.1496,0.0194,0.0108</t>
-  </si>
-  <si>
-    <t>0.9832,0.0180,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9184,0.0576,0.0062,0.0023</t>
-  </si>
-  <si>
-    <t>0.9069,0.0744,0.0072,0.0018</t>
-  </si>
-  <si>
-    <t>0.9795,0.0200,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9222,0.0707,0.0057,0.0014</t>
-  </si>
-  <si>
-    <t>0.9523,0.0446,0.0028,0.0010</t>
-  </si>
-  <si>
-    <t>0.8627,0.1900,0.0028,0.0008</t>
-  </si>
-  <si>
-    <t>0.6944,0.2821,0.0034,0.0015</t>
-  </si>
-  <si>
-    <t>0.3176,0.2427,0.5603,0.0070</t>
-  </si>
-  <si>
-    <t>0.9069,0.0945,0.0041,0.0012</t>
-  </si>
-  <si>
-    <t>0.9115,0.0101,0.1238,0.0003</t>
-  </si>
-  <si>
-    <t>0.9676,0.0099,0.0182,0.0002</t>
-  </si>
-  <si>
-    <t>0.9752,0.0082,0.0096,0.0006</t>
-  </si>
-  <si>
-    <t>0.9491,0.0073,0.0811,0.0005</t>
-  </si>
-  <si>
-    <t>0.9893,0.0035,0.0046,0.0000</t>
-  </si>
-  <si>
-    <t>0.8546,0.0334,0.0892,0.0008</t>
-  </si>
-  <si>
-    <t>0.8762,0.0171,0.1676,0.0019</t>
-  </si>
-  <si>
-    <t>0.9909,0.0020,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.9815,0.0058,0.0070,0.0002</t>
-  </si>
-  <si>
-    <t>0.8780,0.0976,0.0030,0.0006</t>
-  </si>
-  <si>
-    <t>0.9882,0.0063,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9839,0.0073,0.0037,0.0002</t>
-  </si>
-  <si>
-    <t>0.9879,0.0039,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.9922,0.0016,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9798,0.0071,0.0054,0.0004</t>
-  </si>
-  <si>
-    <t>0.8756,0.1343,0.0043,0.0032</t>
-  </si>
-  <si>
-    <t>0.9092,0.1260,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9729,0.0135,0.0043,0.0017</t>
-  </si>
-  <si>
-    <t>0.9275,0.1077,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.8226,0.1916,0.0061,0.0026</t>
-  </si>
-  <si>
-    <t>0.9931,0.0006,0.0053,0.0001</t>
-  </si>
-  <si>
-    <t>0.9948,0.0017,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.9619,0.0063,0.0297,0.0015</t>
-  </si>
-  <si>
-    <t>0.9748,0.0048,0.0166,0.0014</t>
-  </si>
-  <si>
-    <t>0.9837,0.0039,0.0081,0.0001</t>
-  </si>
-  <si>
-    <t>0.9949,0.0009,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.8652,0.0614,0.0501,0.0032</t>
-  </si>
-  <si>
-    <t>0.8630,0.0775,0.0482,0.0020</t>
-  </si>
-  <si>
-    <t>0.8543,0.0563,0.1019,0.0014</t>
-  </si>
-  <si>
-    <t>0.8885,0.0078,0.1905,0.0038</t>
-  </si>
-  <si>
-    <t>0.8251,0.1545,0.0128,0.0056</t>
-  </si>
-  <si>
-    <t>0.8890,0.1104,0.0053,0.0015</t>
-  </si>
-  <si>
-    <t>0.9047,0.0859,0.0063,0.0013</t>
-  </si>
-  <si>
-    <t>0.8719,0.1228,0.0115,0.0045</t>
-  </si>
-  <si>
-    <t>0.9145,0.0831,0.0029,0.0012</t>
-  </si>
-  <si>
-    <t>0.9612,0.0355,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.8685,0.0750,0.0042,0.0077</t>
-  </si>
-  <si>
-    <t>0.9778,0.0137,0.0018,0.0009</t>
-  </si>
-  <si>
-    <t>0.8411,0.0767,0.0679,0.0008</t>
-  </si>
-  <si>
-    <t>0.9693,0.0199,0.0048,0.0004</t>
-  </si>
-  <si>
-    <t>0.9239,0.0771,0.0083,0.0010</t>
-  </si>
-  <si>
-    <t>0.7390,0.0191,0.4394,0.0018</t>
-  </si>
-  <si>
-    <t>0.6406,0.0625,0.3590,0.0014</t>
-  </si>
-  <si>
-    <t>0.7230,0.1233,0.1086,0.0003</t>
-  </si>
-  <si>
-    <t>0.8098,0.0090,0.3746,0.0004</t>
-  </si>
-  <si>
-    <t>0.9559,0.0071,0.0410,0.0003</t>
-  </si>
-  <si>
-    <t>0.7030,0.0490,0.3985,0.0030</t>
-  </si>
-  <si>
-    <t>0.9259,0.0148,0.0959,0.0035</t>
-  </si>
-  <si>
-    <t>0.9864,0.0032,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.9768,0.0056,0.0064,0.0009</t>
-  </si>
-  <si>
-    <t>0.9975,0.0003,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9848,0.0037,0.0041,0.0005</t>
-  </si>
-  <si>
-    <t>0.7967,0.2801,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9216,0.0635,0.0057,0.0029</t>
-  </si>
-  <si>
-    <t>0.9662,0.0212,0.0010,0.0009</t>
-  </si>
-  <si>
-    <t>0.7263,0.1674,0.0111,0.0104</t>
-  </si>
-  <si>
-    <t>0.9512,0.0191,0.0031,0.0047</t>
-  </si>
-  <si>
-    <t>0.9283,0.0611,0.0019,0.0018</t>
-  </si>
-  <si>
-    <t>0.8065,0.1185,0.0152,0.0237</t>
-  </si>
-  <si>
-    <t>0.8343,0.0825,0.0052,0.0064</t>
-  </si>
-  <si>
-    <t>0.8556,0.0534,0.0805,0.0017</t>
-  </si>
-  <si>
-    <t>0.8846,0.0416,0.0799,0.0009</t>
-  </si>
-  <si>
-    <t>0.8666,0.0491,0.0953,0.0023</t>
-  </si>
-  <si>
-    <t>0.9856,0.0066,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.6720,0.0426,0.4082,0.0021</t>
-  </si>
-  <si>
-    <t>0.9818,0.0050,0.0059,0.0004</t>
-  </si>
-  <si>
-    <t>0.9972,0.0004,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.4259,0.4415,0.1972,0.0057</t>
-  </si>
-  <si>
-    <t>0.9827,0.0039,0.0021,0.0022</t>
-  </si>
-  <si>
-    <t>0.9506,0.0108,0.0289,0.0056</t>
-  </si>
-  <si>
-    <t>0.9710,0.0070,0.0096,0.0017</t>
-  </si>
-  <si>
-    <t>0.9813,0.0008,0.0131,0.0022</t>
-  </si>
-  <si>
-    <t>0.9658,0.0035,0.0122,0.0060</t>
-  </si>
-  <si>
-    <t>0.9695,0.0158,0.0056,0.0006</t>
+    <t>0.9449,0.0329,0.0053,0.0143</t>
+  </si>
+  <si>
+    <t>0.0239,0.0036,0.0033,0.9851</t>
+  </si>
+  <si>
+    <t>0.5973,0.0048,0.0016,0.4743</t>
+  </si>
+  <si>
+    <t>0.0440,0.0083,0.0056,0.9722</t>
+  </si>
+  <si>
+    <t>0.9971,0.0009,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9978,0.0008,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9949,0.0027,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9618,0.0258,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9960,0.0026,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9894,0.0073,0.0018,0.0024</t>
+  </si>
+  <si>
+    <t>0.9938,0.0074,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.8416,0.0130,0.1732,0.0105</t>
+  </si>
+  <si>
+    <t>0.3924,0.0047,0.7691,0.0011</t>
+  </si>
+  <si>
+    <t>0.2474,0.0115,0.8466,0.0017</t>
+  </si>
+  <si>
+    <t>0.1278,0.0415,0.7947,0.0035</t>
+  </si>
+  <si>
+    <t>0.8071,0.0077,0.2759,0.0013</t>
+  </si>
+  <si>
+    <t>0.0049,0.9927,0.0025,0.0010</t>
+  </si>
+  <si>
+    <t>0.0042,0.9955,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.0264,0.9807,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.0221,0.9866,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.9978,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.7380,0.0083,0.2324,0.0436</t>
+  </si>
+  <si>
+    <t>0.0571,0.0093,0.9364,0.0018</t>
+  </si>
+  <si>
+    <t>0.0265,0.0312,0.9369,0.0231</t>
+  </si>
+  <si>
+    <t>0.0170,0.0076,0.9533,0.0124</t>
+  </si>
+  <si>
+    <t>0.1321,0.0696,0.8724,0.0108</t>
+  </si>
+  <si>
+    <t>0.1275,0.0053,0.8930,0.0067</t>
+  </si>
+  <si>
+    <t>0.0047,0.0021,0.9906,0.0028</t>
+  </si>
+  <si>
+    <t>0.0312,0.9680,0.0081,0.0012</t>
+  </si>
+  <si>
+    <t>0.6630,0.2413,0.1291,0.0254</t>
+  </si>
+  <si>
+    <t>0.0010,0.0039,0.9919,0.0089</t>
+  </si>
+  <si>
+    <t>0.0360,0.9335,0.0377,0.0124</t>
+  </si>
+  <si>
+    <t>0.9054,0.0446,0.0290,0.0247</t>
+  </si>
+  <si>
+    <t>0.9069,0.0094,0.0982,0.0023</t>
+  </si>
+  <si>
+    <t>0.9045,0.1813,0.0036,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.9935,0.2635,0.0005</t>
+  </si>
+  <si>
+    <t>0.0056,0.8654,0.0536,0.0737</t>
+  </si>
+  <si>
+    <t>0.3098,0.0012,0.8598,0.0020</t>
+  </si>
+  <si>
+    <t>0.1179,0.0319,0.8735,0.0133</t>
+  </si>
+  <si>
+    <t>0.0517,0.0023,0.9121,0.0322</t>
+  </si>
+  <si>
+    <t>0.0069,0.0251,0.9806,0.0016</t>
+  </si>
+  <si>
+    <t>0.0050,0.9641,0.0169,0.0048</t>
+  </si>
+  <si>
+    <t>0.0010,0.0139,0.9921,0.0013</t>
+  </si>
+  <si>
+    <t>0.2498,0.3026,0.1829,0.5599</t>
+  </si>
+  <si>
+    <t>0.0088,0.9797,0.0027,0.0274</t>
+  </si>
+  <si>
+    <t>0.0011,0.9960,0.0061,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.9959,0.0068,0.0005</t>
+  </si>
+  <si>
+    <t>0.0248,0.0054,0.9769,0.0020</t>
+  </si>
+  <si>
+    <t>0.0015,0.1466,0.9943,0.0005</t>
+  </si>
+  <si>
+    <t>0.0376,0.0069,0.9481,0.0127</t>
+  </si>
+  <si>
+    <t>0.1131,0.0223,0.8730,0.0158</t>
+  </si>
+  <si>
+    <t>0.0114,0.0616,0.9832,0.0007</t>
+  </si>
+  <si>
+    <t>0.0007,0.0044,0.9955,0.0021</t>
+  </si>
+  <si>
+    <t>0.8528,0.2350,0.0090,0.0031</t>
+  </si>
+  <si>
+    <t>0.9846,0.0062,0.0044,0.0030</t>
+  </si>
+  <si>
+    <t>0.9663,0.0299,0.0075,0.0024</t>
+  </si>
+  <si>
+    <t>0.0077,0.0596,0.9799,0.0119</t>
+  </si>
+  <si>
+    <t>0.9844,0.0176,0.0039,0.0010</t>
+  </si>
+  <si>
+    <t>0.9924,0.0049,0.0014,0.0012</t>
+  </si>
+  <si>
+    <t>0.9812,0.0216,0.0036,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.8851,0.9596,0.0005</t>
+  </si>
+  <si>
+    <t>0.0132,0.4430,0.9502,0.0027</t>
+  </si>
+  <si>
+    <t>0.0009,0.0090,0.9915,0.0028</t>
+  </si>
+  <si>
+    <t>0.0058,0.7805,0.9401,0.0016</t>
+  </si>
+  <si>
+    <t>0.0053,0.0128,0.9902,0.0011</t>
+  </si>
+  <si>
+    <t>0.0714,0.9430,0.0136,0.0008</t>
+  </si>
+  <si>
+    <t>0.0042,0.9974,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8276,0.0771,0.1752,0.0090</t>
+  </si>
+  <si>
+    <t>0.7694,0.1863,0.0862,0.0147</t>
+  </si>
+  <si>
+    <t>0.0031,0.0194,0.9936,0.0011</t>
+  </si>
+  <si>
+    <t>0.0024,0.8077,0.9196,0.0005</t>
+  </si>
+  <si>
+    <t>0.0034,0.8494,0.9303,0.0006</t>
+  </si>
+  <si>
+    <t>0.0013,0.9949,0.0189,0.0013</t>
+  </si>
+  <si>
+    <t>0.0004,0.9921,0.7049,0.0002</t>
+  </si>
+  <si>
+    <t>0.0038,0.0012,0.0129,0.9933</t>
+  </si>
+  <si>
+    <t>0.0009,0.0009,0.0006,0.9990</t>
+  </si>
+  <si>
+    <t>0.0086,0.0020,0.0014,0.9948</t>
+  </si>
+  <si>
+    <t>0.0389,0.0029,0.0039,0.9817</t>
+  </si>
+  <si>
+    <t>0.0006,0.0026,0.0038,0.9981</t>
+  </si>
+  <si>
+    <t>0.0005,0.0637,0.0009,0.9972</t>
+  </si>
+  <si>
+    <t>0.0001,0.9916,0.9505,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9146,0.9895,0.0000</t>
+  </si>
+  <si>
+    <t>0.0436,0.6907,0.3787,0.0081</t>
+  </si>
+  <si>
+    <t>0.0057,0.3460,0.9687,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.9843,0.9546,0.0001</t>
+  </si>
+  <si>
+    <t>0.0080,0.8274,0.4110,0.0019</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9930,0.0061,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9954,0.0042,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9897,0.0040,0.0011,0.0027</t>
+  </si>
+  <si>
+    <t>0.9931,0.0055,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9864,0.0162,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9862,0.0092,0.0009,0.0017</t>
+  </si>
+  <si>
+    <t>0.9959,0.0031,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0005,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0006,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9957,0.0009,0.0005,0.0023</t>
+  </si>
+  <si>
+    <t>0.9957,0.0016,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.9950,0.0029,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9972,0.0015,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0116,0.0108,0.9877,0.0024</t>
+  </si>
+  <si>
+    <t>0.0215,0.7008,0.8062,0.0085</t>
+  </si>
+  <si>
+    <t>0.8621,0.0298,0.0339,0.0596</t>
+  </si>
+  <si>
+    <t>0.0235,0.0373,0.9757,0.0013</t>
+  </si>
+  <si>
+    <t>0.1624,0.9081,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.0310,0.9754,0.0020,0.0009</t>
+  </si>
+  <si>
+    <t>0.1139,0.9094,0.0029,0.0037</t>
+  </si>
+  <si>
+    <t>0.0061,0.9932,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.0107,0.9880,0.0023,0.0010</t>
+  </si>
+  <si>
+    <t>0.0051,0.9939,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9255,0.1228,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.4138,0.0715,0.5475,0.0176</t>
+  </si>
+  <si>
+    <t>0.1057,0.0056,0.9177,0.0019</t>
+  </si>
+  <si>
+    <t>0.5496,0.1646,0.3003,0.0588</t>
+  </si>
+  <si>
+    <t>0.4767,0.0131,0.6236,0.0092</t>
+  </si>
+  <si>
+    <t>0.6599,0.1245,0.1453,0.1664</t>
+  </si>
+  <si>
+    <t>0.0030,0.9922,0.0037,0.0013</t>
+  </si>
+  <si>
+    <t>0.0008,0.9965,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.9982,0.0045,0.0119</t>
+  </si>
+  <si>
+    <t>0.0020,0.9718,0.5477,0.0006</t>
+  </si>
+  <si>
+    <t>0.0014,0.9983,0.0041,0.0000</t>
+  </si>
+  <si>
+    <t>0.8812,0.1236,0.0137,0.0006</t>
+  </si>
+  <si>
+    <t>0.1914,0.8762,0.0086,0.0004</t>
+  </si>
+  <si>
+    <t>0.9570,0.0670,0.0053,0.0006</t>
+  </si>
+  <si>
+    <t>0.9846,0.0060,0.0046,0.0038</t>
+  </si>
+  <si>
+    <t>0.9915,0.0032,0.0020,0.0017</t>
+  </si>
+  <si>
+    <t>0.9579,0.0472,0.0084,0.0020</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9971,0.0021,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9853,0.0039,0.0038,0.0064</t>
+  </si>
+  <si>
+    <t>0.9893,0.0051,0.0026,0.0019</t>
+  </si>
+  <si>
+    <t>0.0070,0.4763,0.9267,0.0038</t>
+  </si>
+  <si>
+    <t>0.0020,0.8727,0.8656,0.0005</t>
+  </si>
+  <si>
+    <t>0.0033,0.0713,0.9775,0.0011</t>
+  </si>
+  <si>
+    <t>0.0114,0.0750,0.9804,0.0004</t>
+  </si>
+  <si>
+    <t>0.9954,0.0008,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.8922,0.0025,0.1327,0.0046</t>
+  </si>
+  <si>
+    <t>0.0454,0.0012,0.9603,0.0037</t>
+  </si>
+  <si>
+    <t>0.7010,0.0124,0.3495,0.0153</t>
+  </si>
+  <si>
+    <t>0.0478,0.0109,0.0031,0.9729</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.0009,0.9995</t>
+  </si>
+  <si>
+    <t>0.0006,0.0036,0.0005,0.9991</t>
+  </si>
+  <si>
+    <t>0.0010,0.0013,0.0008,0.9987</t>
+  </si>
+  <si>
+    <t>0.0016,0.9548,0.1906,0.0018</t>
+  </si>
+  <si>
+    <t>0.9658,0.0208,0.0099,0.0054</t>
+  </si>
+  <si>
+    <t>0.0766,0.9367,0.0031,0.0045</t>
+  </si>
+  <si>
+    <t>0.9803,0.0067,0.0050,0.0056</t>
+  </si>
+  <si>
+    <t>0.7484,0.4180,0.0016,0.0017</t>
+  </si>
+  <si>
+    <t>0.9518,0.0164,0.0115,0.0122</t>
+  </si>
+  <si>
+    <t>0.3027,0.0141,0.0073,0.7678</t>
+  </si>
+  <si>
+    <t>0.9853,0.0040,0.0030,0.0036</t>
+  </si>
+  <si>
+    <t>0.0139,0.0172,0.9629,0.0331</t>
+  </si>
+  <si>
+    <t>0.8269,0.0013,0.0110,0.1304</t>
+  </si>
+  <si>
+    <t>0.8329,0.0248,0.0597,0.1116</t>
+  </si>
+  <si>
+    <t>0.5002,0.4770,0.0689,0.0047</t>
+  </si>
+  <si>
+    <t>0.9755,0.0119,0.0004,0.0037</t>
+  </si>
+  <si>
+    <t>0.9938,0.0031,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.2334,0.7763,0.0418,0.0117</t>
+  </si>
+  <si>
+    <t>0.6349,0.2603,0.1301,0.0138</t>
+  </si>
+  <si>
+    <t>0.9545,0.0477,0.0037,0.0006</t>
+  </si>
+  <si>
+    <t>0.9884,0.0079,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.9928,0.0032,0.0009,0.0016</t>
+  </si>
+  <si>
+    <t>0.9891,0.0026,0.0024,0.0035</t>
+  </si>
+  <si>
+    <t>0.9925,0.0005,0.0001,0.0056</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9898,0.0030,0.0050,0.0010</t>
+  </si>
+  <si>
+    <t>0.9828,0.0103,0.0005,0.0021</t>
+  </si>
+  <si>
+    <t>0.9919,0.0010,0.0004,0.0042</t>
+  </si>
+  <si>
+    <t>0.8792,0.2927,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.3740,0.7323,0.0104,0.0012</t>
+  </si>
+  <si>
+    <t>0.7979,0.2843,0.0059,0.0015</t>
+  </si>
+  <si>
+    <t>0.8197,0.1321,0.0123,0.0137</t>
+  </si>
+  <si>
+    <t>0.9769,0.0185,0.0026,0.0033</t>
+  </si>
+  <si>
+    <t>0.9556,0.0425,0.0036,0.0054</t>
+  </si>
+  <si>
+    <t>0.9940,0.0026,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.9281,0.0997,0.0048,0.0024</t>
+  </si>
+  <si>
+    <t>0.0004,0.0340,0.9976,0.0005</t>
+  </si>
+  <si>
+    <t>0.7297,0.1929,0.0243,0.0016</t>
+  </si>
+  <si>
+    <t>0.0006,0.0099,0.9969,0.0003</t>
+  </si>
+  <si>
+    <t>0.0398,0.0835,0.9287,0.0093</t>
+  </si>
+  <si>
+    <t>0.0736,0.0120,0.9326,0.0018</t>
+  </si>
+  <si>
+    <t>0.0072,0.0260,0.9894,0.0024</t>
+  </si>
+  <si>
+    <t>0.0059,0.0247,0.9837,0.0012</t>
+  </si>
+  <si>
+    <t>0.0044,0.0011,0.9954,0.0004</t>
+  </si>
+  <si>
+    <t>0.0023,0.0093,0.9912,0.0024</t>
+  </si>
+  <si>
+    <t>0.2436,0.0274,0.7906,0.0040</t>
+  </si>
+  <si>
+    <t>0.0493,0.0138,0.9183,0.0097</t>
+  </si>
+  <si>
+    <t>0.4362,0.0251,0.6277,0.0075</t>
+  </si>
+  <si>
+    <t>0.3422,0.0204,0.6696,0.0003</t>
+  </si>
+  <si>
+    <t>0.2202,0.1121,0.6536,0.0031</t>
+  </si>
+  <si>
+    <t>0.1189,0.3520,0.4603,0.0919</t>
+  </si>
+  <si>
+    <t>0.5621,0.0462,0.4155,0.0594</t>
+  </si>
+  <si>
+    <t>0.2107,0.0504,0.7782,0.0053</t>
+  </si>
+  <si>
+    <t>0.9291,0.0970,0.0078,0.0011</t>
+  </si>
+  <si>
+    <t>0.9292,0.1846,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9602,0.0521,0.0053,0.0016</t>
+  </si>
+  <si>
+    <t>0.9611,0.0656,0.0035,0.0012</t>
+  </si>
+  <si>
+    <t>0.9181,0.1918,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.2717,0.1806,0.6162,0.0380</t>
+  </si>
+  <si>
+    <t>0.9779,0.0029,0.0249,0.0006</t>
+  </si>
+  <si>
+    <t>0.9118,0.0103,0.0268,0.0390</t>
+  </si>
+  <si>
+    <t>0.8308,0.0033,0.2051,0.0073</t>
+  </si>
+  <si>
+    <t>0.2420,0.0151,0.6602,0.0736</t>
+  </si>
+  <si>
+    <t>0.0358,0.0210,0.8870,0.0744</t>
+  </si>
+  <si>
+    <t>0.1895,0.2091,0.6852,0.0208</t>
+  </si>
+  <si>
+    <t>0.0067,0.8635,0.8337,0.0289</t>
+  </si>
+  <si>
+    <t>0.5310,0.0265,0.5354,0.0051</t>
+  </si>
+  <si>
+    <t>0.0033,0.4238,0.7128,0.0108</t>
+  </si>
+  <si>
+    <t>0.9935,0.0034,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9793,0.0133,0.0044,0.0048</t>
+  </si>
+  <si>
+    <t>0.9892,0.0127,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9820,0.0399,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9829,0.0152,0.0017,0.0022</t>
+  </si>
+  <si>
+    <t>0.9959,0.0037,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9747,0.0184,0.0046,0.0035</t>
+  </si>
+  <si>
+    <t>0.9969,0.0005,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.0052,0.0139,0.9857,0.0091</t>
+  </si>
+  <si>
+    <t>0.0734,0.4913,0.5960,0.0113</t>
+  </si>
+  <si>
+    <t>0.9679,0.0090,0.0166,0.0032</t>
+  </si>
+  <si>
+    <t>0.0031,0.0016,0.9946,0.0007</t>
+  </si>
+  <si>
+    <t>0.0053,0.0094,0.9798,0.0133</t>
+  </si>
+  <si>
+    <t>0.0047,0.2043,0.9333,0.0067</t>
+  </si>
+  <si>
+    <t>0.0051,0.0044,0.9948,0.0004</t>
+  </si>
+  <si>
+    <t>0.2512,0.0385,0.7555,0.0027</t>
+  </si>
+  <si>
+    <t>0.0037,0.0025,0.9964,0.0004</t>
+  </si>
+  <si>
+    <t>0.2171,0.0484,0.7925,0.0211</t>
+  </si>
+  <si>
+    <t>0.2032,0.1546,0.6383,0.0066</t>
+  </si>
+  <si>
+    <t>0.7379,0.0031,0.2425,0.0186</t>
+  </si>
+  <si>
+    <t>0.7989,0.0006,0.3602,0.0028</t>
+  </si>
+  <si>
+    <t>0.8482,0.0092,0.1355,0.0205</t>
+  </si>
+  <si>
+    <t>0.9911,0.0058,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9926,0.0053,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.9939,0.0039,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.9909,0.0096,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9907,0.0112,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9964,0.0010,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9940,0.0037,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.0081,0.2746,0.8992,0.0023</t>
+  </si>
+  <si>
+    <t>0.0053,0.0282,0.9825,0.0010</t>
+  </si>
+  <si>
+    <t>0.0078,0.0444,0.9761,0.0036</t>
+  </si>
+  <si>
+    <t>0.0215,0.0403,0.9163,0.0068</t>
+  </si>
+  <si>
+    <t>0.1289,0.0019,0.9374,0.0033</t>
+  </si>
+  <si>
+    <t>0.4389,0.0597,0.5692,0.0381</t>
+  </si>
+  <si>
+    <t>0.0364,0.1298,0.9275,0.0183</t>
+  </si>
+  <si>
+    <t>0.0207,0.0923,0.9563,0.0051</t>
+  </si>
+  <si>
+    <t>0.8187,0.0011,0.0031,0.2191</t>
+  </si>
+  <si>
+    <t>0.0147,0.0093,0.0078,0.9852</t>
+  </si>
+  <si>
+    <t>0.5585,0.0047,0.0063,0.6047</t>
+  </si>
+  <si>
+    <t>0.0017,0.0003,0.0024,0.9982</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.0005,0.9996</t>
+  </si>
+  <si>
+    <t>0.9606,0.0068,0.0236,0.0113</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3549,7 +3549,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
         <v>378</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4767,7 +4767,7 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D203" t="s">
         <v>465</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5103,7 +5103,7 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
         <v>489</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5131,7 +5131,7 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D229" t="s">
         <v>491</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
